--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/utils/emailRegex-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/utils/emailRegex-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="126">
-  <si>
-    <t>Statement: emailRegex – pattern /^[^\s@]+@[^\s@]+\.[^\s@]+$/ validates simplified RFC 5321 email addresses.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="125">
+  <si>
+    <t>Statement: emailRegex – Tests whether a string matches the pattern /^[^\s@]+@[^\s@]+\.[^\s@]+$/. Returns true when the string contains exactly one "@" separating a non-empty local part from a domain that itself contains at least one "." with non-empty segments on both sides, and no whitespace anywhere. Returns false for any deviation: missing "@", empty local part, missing or empty domain, no "." in domain, trailing dot, spaces, multiple "@" symbols, or empty input.</t>
   </si>
   <si>
     <t/>
@@ -31,25 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: string s</t>
+    <t>Input: string s passed to emailRegex.test(s)</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>None</t>
+    <t>No preconditions. The regex is applied directly to the input string.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: boolean</t>
+    <t>Output: boolean — true if the string matches /^[^\s@]+@[^\s@]+\.[^\s@]+$/, false otherwise.</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>True if format matches.</t>
+    <t>Result reflects structural conformance only. DNS existence or full RFC 5321 compliance is not checked.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,106 +64,106 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>Basic email</t>
-  </si>
-  <si>
-    <t>user@example.com</t>
-  </si>
-  <si>
-    <t>Subdomain</t>
-  </si>
-  <si>
-    <t>user@mail.example.com</t>
-  </si>
-  <si>
-    <t>Plus tag</t>
-  </si>
-  <si>
-    <t>user+tag@domain.com</t>
-  </si>
-  <si>
-    <t>Dot in local</t>
-  </si>
-  <si>
-    <t>first.last@domain.com</t>
-  </si>
-  <si>
-    <t>Numeric local</t>
-  </si>
-  <si>
-    <t>12345@domain.com</t>
-  </si>
-  <si>
-    <t>Special local</t>
-  </si>
-  <si>
-    <t>user.name+tag@example.org</t>
-  </si>
-  <si>
-    <t>No at symbol</t>
-  </si>
-  <si>
-    <t>invalidemail.com</t>
-  </si>
-  <si>
-    <t>Empty local</t>
-  </si>
-  <si>
-    <t>@domain.com</t>
-  </si>
-  <si>
-    <t>No domain after @</t>
-  </si>
-  <si>
-    <t>user@</t>
-  </si>
-  <si>
-    <t>No dot in domain</t>
-  </si>
-  <si>
-    <t>user@domain</t>
-  </si>
-  <si>
-    <t>Space in local</t>
-  </si>
-  <si>
-    <t>user name@domain.com</t>
-  </si>
-  <si>
-    <t>Space after @</t>
-  </si>
-  <si>
-    <t>user@ domain.com</t>
-  </si>
-  <si>
-    <t>Multiple @ symbols</t>
-  </si>
-  <si>
-    <t>a@b@example.com</t>
-  </si>
-  <si>
-    <t>Empty domain before dot</t>
-  </si>
-  <si>
-    <t>user@.com</t>
-  </si>
-  <si>
-    <t>Trailing dot</t>
-  </si>
-  <si>
-    <t>user@domain.</t>
+    <t>Standard valid email</t>
+  </si>
+  <si>
+    <t>"user@example.com" → true</t>
+  </si>
+  <si>
+    <t>Subdomain in domain part</t>
+  </si>
+  <si>
+    <t>"user@mail.example.com" → true</t>
+  </si>
+  <si>
+    <t>Plus tag in local part</t>
+  </si>
+  <si>
+    <t>"user+tag@domain.com" → true</t>
+  </si>
+  <si>
+    <t>Dot in local part</t>
+  </si>
+  <si>
+    <t>"first.last@domain.com" → true</t>
+  </si>
+  <si>
+    <t>Numeric local part</t>
+  </si>
+  <si>
+    <t>"12345@domain.com" → true</t>
+  </si>
+  <si>
+    <t>Special chars in local part</t>
+  </si>
+  <si>
+    <t>"user.name+tag@example.org" → true</t>
+  </si>
+  <si>
+    <t>"@" symbol presence</t>
+  </si>
+  <si>
+    <t>"invalidemail.com" (no "@" symbol) → false</t>
+  </si>
+  <si>
+    <t>Non-empty local part</t>
+  </si>
+  <si>
+    <t>"@domain.com" (empty local part) → false</t>
+  </si>
+  <si>
+    <t>Non-empty domain part</t>
+  </si>
+  <si>
+    <t>"user@" (no domain after "@") → false</t>
+  </si>
+  <si>
+    <t>"." in domain part</t>
+  </si>
+  <si>
+    <t>"user@domain" (no dot in domain) → false</t>
+  </si>
+  <si>
+    <t>No whitespace in local part</t>
+  </si>
+  <si>
+    <t>"user name@domain.com" (space in local part) → false</t>
+  </si>
+  <si>
+    <t>No whitespace after "@"</t>
+  </si>
+  <si>
+    <t>"user@ domain.com" (space after "@") → false</t>
+  </si>
+  <si>
+    <t>Exactly one "@" symbol</t>
+  </si>
+  <si>
+    <t>"a@b@example.com" (multiple "@" symbols) → false</t>
+  </si>
+  <si>
+    <t>Non-empty segment before "."</t>
+  </si>
+  <si>
+    <t>"user@.com" (empty domain segment before dot) → false</t>
+  </si>
+  <si>
+    <t>Non-empty segment after "."</t>
+  </si>
+  <si>
+    <t>"user@domain." (trailing dot, empty TLD) → false</t>
   </si>
   <si>
     <t>Empty string</t>
   </si>
   <si>
-    <t>""</t>
-  </si>
-  <si>
-    <t>At symbol only</t>
-  </si>
-  <si>
-    <t>@</t>
+    <t>"" (empty string) → false</t>
+  </si>
+  <si>
+    <t>"@" symbol alone</t>
+  </si>
+  <si>
+    <t>"@" (at symbol only) → false</t>
   </si>
   <si>
     <t>No TC</t>
@@ -283,10 +283,13 @@
     <t>EC-16</t>
   </si>
   <si>
+    <t>"" (empty string)</t>
+  </si>
+  <si>
     <t>EC-17</t>
   </si>
   <si>
-    <t>"@"</t>
+    <t>"@" (at symbol only)</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -304,55 +307,49 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>"user@example.com" (Standard)</t>
-  </si>
-  <si>
-    <t>"user@mail.example.com" (Subdomain)</t>
-  </si>
-  <si>
-    <t>"user+tag@domain.com" (Plus tag)</t>
-  </si>
-  <si>
-    <t>"first.last@domain.com" (Dot in local)</t>
-  </si>
-  <si>
-    <t>"12345@domain.com" (Numeric local)</t>
-  </si>
-  <si>
-    <t>"user.name+tag@example.org" (Special local)</t>
-  </si>
-  <si>
-    <t>"invalidemail.com" (No @)</t>
-  </si>
-  <si>
-    <t>"@domain.com" (Empty local)</t>
-  </si>
-  <si>
-    <t>"user@" (No domain)</t>
-  </si>
-  <si>
-    <t>"user@domain" (No dot in domain)</t>
-  </si>
-  <si>
-    <t>"user name@domain.com" (Space in local)</t>
-  </si>
-  <si>
-    <t>"user@ domain.com" (Space after @)</t>
-  </si>
-  <si>
-    <t>"a@b@example.com" (Multiple @)</t>
-  </si>
-  <si>
-    <t>"user@.com" (Empty domain before dot)</t>
-  </si>
-  <si>
-    <t>"user@domain." (Trailing dot)</t>
-  </si>
-  <si>
-    <t>"" (Empty string)</t>
-  </si>
-  <si>
-    <t>"@" (At symbol only)</t>
+    <t>"user@example.com" (standard valid email)</t>
+  </si>
+  <si>
+    <t>"user@mail.example.com" (subdomain in domain part)</t>
+  </si>
+  <si>
+    <t>"user+tag@domain.com" (plus tag in local part)</t>
+  </si>
+  <si>
+    <t>"first.last@domain.com" (dot in local part)</t>
+  </si>
+  <si>
+    <t>"12345@domain.com" (numeric local part)</t>
+  </si>
+  <si>
+    <t>"user.name+tag@example.org" (special chars in local)</t>
+  </si>
+  <si>
+    <t>"invalidemail.com" (no "@" symbol)</t>
+  </si>
+  <si>
+    <t>"@domain.com" (empty local part)</t>
+  </si>
+  <si>
+    <t>"user@" (no domain after "@")</t>
+  </si>
+  <si>
+    <t>"user@domain" (no dot in domain)</t>
+  </si>
+  <si>
+    <t>"user name@domain.com" (space in local part)</t>
+  </si>
+  <si>
+    <t>"user@ domain.com" (space after "@")</t>
+  </si>
+  <si>
+    <t>"a@b@example.com" (multiple "@" symbols)</t>
+  </si>
+  <si>
+    <t>"user@.com" (empty domain segment before dot)</t>
+  </si>
+  <si>
+    <t>"user@domain." (trailing dot, empty TLD)</t>
   </si>
   <si>
     <t>Testing</t>
@@ -385,7 +382,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>UTILS-EMAIL</t>
+    <t>SCHEMA-16</t>
   </si>
   <si>
     <t>n/a</t>
@@ -1468,7 +1465,7 @@
         <v>87</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>70</v>
@@ -1482,10 +1479,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>70</v>
@@ -1512,13 +1509,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1544,7 +1541,7 @@
         <v>49</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>51</v>
@@ -1580,10 +1577,10 @@
         <v>49</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>51</v>
@@ -1606,7 +1603,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>56</v>
@@ -1626,7 +1623,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>56</v>
@@ -1646,7 +1643,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>56</v>
@@ -1666,7 +1663,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>56</v>
@@ -1686,7 +1683,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>56</v>
@@ -1706,7 +1703,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>56</v>
@@ -1726,7 +1723,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>70</v>
@@ -1746,7 +1743,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>70</v>
@@ -1766,7 +1763,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>70</v>
@@ -1786,7 +1783,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>70</v>
@@ -1806,7 +1803,7 @@
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>70</v>
@@ -1826,7 +1823,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>70</v>
@@ -1846,7 +1843,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>70</v>
@@ -1866,7 +1863,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>70</v>
@@ -1886,7 +1883,7 @@
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>70</v>
@@ -1906,7 +1903,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>70</v>
@@ -1920,13 +1917,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>70</v>
@@ -1960,16 +1957,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1977,39 +1974,39 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>121</v>
-      </c>
       <c r="H2" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B3" s="1">
         <v>17</v>
@@ -2024,19 +2021,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>124</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/utils/emailRegex-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/utils/emailRegex-bbt-form.xlsx
@@ -382,7 +382,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>SCHEMA-16</t>
+    <t>SCHEMA-18</t>
   </si>
   <si>
     <t>n/a</t>

--- a/Exam/gymtrackerpro/lib/schema/__tests__/bbt/utils/emailRegex-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/schema/__tests__/bbt/utils/emailRegex-bbt-form.xlsx
@@ -382,7 +382,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>SCHEMA-18</t>
+    <t>SCHEMA-20</t>
   </si>
   <si>
     <t>n/a</t>
